--- a/ig/ch-vacd/StructureDefinition-ch-vacd-ext-immunization-medication-reference.xlsx
+++ b/ig/ch-vacd/StructureDefinition-ch-vacd-ext-immunization-medication-reference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
